--- a/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260803.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/0056/ETF_Investment_Portfolio_20260803.xlsx
@@ -711,17 +711,17 @@
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
         <is>
-          <t>2886</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>兆豐金</t>
+          <t>華碩</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>548,837,368</t>
+          <t>35,436,792</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
@@ -733,17 +733,17 @@
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
         <is>
-          <t>2357</t>
+          <t>2886</t>
         </is>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>華碩</t>
+          <t>兆豐金</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>35,436,792</t>
+          <t>548,837,368</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
